--- a/artfynd/S 1893-2020 artfynd.xlsx
+++ b/artfynd/S 1893-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,32 +804,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127311655</v>
+        <v>137390394</v>
       </c>
       <c r="B3" t="n">
-        <v>9596</v>
+        <v>9424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101479</v>
+        <v>101246</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Osmoderma eremita</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,32 +837,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>hästö, Karlskrona, Bl</t>
+          <t>Hästö, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538580</v>
+        <v>538711</v>
       </c>
       <c r="R3" t="n">
-        <v>6226507</v>
+        <v>6226571</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,22 +878,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>En död hane utan bakkropp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,75 +907,88 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>peter marton</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>peter marton</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127311655</t>
+          <t>https://artportalen.se/Sighting/137390394</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62657080</v>
+        <v>127311655</v>
       </c>
       <c r="B4" t="n">
-        <v>111176</v>
+        <v>9596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219677</v>
+        <v>101479</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Osmoderma eremita</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogsbacke Herrgårdsvägen, Bl</t>
+          <t>hästö, Karlskrona, Bl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538563</v>
+        <v>538580</v>
       </c>
       <c r="R4" t="n">
-        <v>6226514</v>
+        <v>6226507</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,12 +1012,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-12-26</t>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-12-26</t>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,33 +1036,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan-Åke Rosén</t>
+          <t>peter marton</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan-Åke Rosén</t>
+          <t>peter marton</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62657080</t>
+          <t>https://artportalen.se/Sighting/127311655</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132617408</v>
+        <v>62657080</v>
       </c>
       <c r="B5" t="n">
-        <v>104880</v>
+        <v>111176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,36 +1071,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220460</v>
+        <v>219677</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tandrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cardamine bulbifera</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skogsbacke Herrgårdsvägen, Bl</t>
@@ -1116,12 +1128,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2016-12-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2016-12-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,7 +1142,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1148,54 +1159,66 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132617408</t>
+          <t>https://artportalen.se/Sighting/62657080</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3925949</v>
+        <v>132617408</v>
       </c>
       <c r="B6" t="n">
-        <v>102225</v>
+        <v>104880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221223</v>
+        <v>220460</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Tandrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Cardamine bulbifera</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästö, skog S Oskarsvärnskärret, Bl</t>
+          <t>Skogsbacke Herrgårdsvägen, Bl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538583</v>
+        <v>538563</v>
       </c>
       <c r="R6" t="n">
-        <v>6226605</v>
+        <v>6226514</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,17 +1242,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2010-08-03</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2010-08-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>spridd</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,84 +1256,72 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>ädellövskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Åke Widgren</t>
+          <t>Jan-Åke Rosén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Åke Widgren</t>
+          <t>Jan-Åke Rosén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3925949</t>
+          <t>https://artportalen.se/Sighting/132617408</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132617395</v>
+        <v>3925949</v>
       </c>
       <c r="B7" t="n">
-        <v>101159</v>
+        <v>102225</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222817</v>
+        <v>221223</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smånunneört</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Corydalis intermedia</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Mérat</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skogsbacke Herrgårdsvägen, Bl</t>
+          <t>Hästö, skog S Oskarsvärnskärret, Bl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538563</v>
+        <v>538583</v>
       </c>
       <c r="R7" t="n">
-        <v>6226514</v>
+        <v>6226605</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,17 +1345,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2010-08-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2010-08-03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>antal minst</t>
+          <t>spridd</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,23 +1364,143 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>ädellövskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan-Åke Rosén</t>
+          <t>Åke Widgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan-Åke Rosén</t>
+          <t>Åke Widgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3925949</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132617395</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101159</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222817</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Smånunneört</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Corydalis intermedia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Mérat</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogsbacke Herrgårdsvägen, Bl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>538563</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6226514</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>antal minst</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan-Åke Rosén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan-Åke Rosén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132617395</t>
         </is>
@@ -1388,6 +1514,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
